--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1125,6 +1125,91 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>09:31:55</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10:02:54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>24050</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>14020</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>24101.3</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>2769</v>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>retest | SMA+2 Flow+3 | Nifty@24101 | CE@24050 ITM24050 | NORMAL ATR=30 | risk=₹2340 (4.4%)</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W8" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1210,6 +1210,456 @@
       </c>
       <c r="W8" s="2" t="n"/>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>10:50:36</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>11:19:08</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>23950</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>167.2</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>20527</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>193.9</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>23944.2</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>1209</v>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>retest | SMA+2 Flow+1 | Nifty@23944 | CE@23950 | NORMAL ATR=28 | risk=₹2340 (4.2%)</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="X9" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>11:40:00</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>12:00:20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>150.8</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>18870</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>23983.5</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>728</v>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@23984 | CE@24000 | NORMAL ATR=28 | risk=₹2334 (4.1%)</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="X10" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>12:10:20</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>12:29:26</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>18941</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>127.7</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>23984.5</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>494</v>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@23985 | CE@24000 | NORMAL ATR=28 | risk=₹2340 (4.1%)</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="X11" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>12:30:58</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>13:17:07</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>9496</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>23984.7</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@23985 | CE@24000 | NORMAL ATR=28 | risk=₹2340 (4.0%)</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>partial_target_partial</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="X12" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>12:30:58</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>14:12:08</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>9496</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>226.4</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>23984.7</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>2386</v>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@23985 | CE@24000 | NORMAL ATR=28 | risk=₹2340 (4.0%)</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>manual_exit</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="X13" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1660,6 +1660,456 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>09:30:01</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>10:01:43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>24150</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>15086</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>152.1</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>24148.7</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>1170</v>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24149 | CE@24150 | NORMAL ATR=28 | risk=₹2346 (3.7%)</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="X14" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>10:01:44</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>10:17:37</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>24150</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>16341</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>161.7</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>24169</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>-13</v>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24169 | CE@24150 | NORMAL ATR=28 | risk=₹2340 (3.7%)</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="X15" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>10:17:57</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>11:30:47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>24150</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>16250</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>24174.7</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>1170</v>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24175 | CE@24150 | NORMAL ATR=28 | risk=₹2340 (3.7%)</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="X16" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>13:14:38</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>13:47:06</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>24150</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>16523</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>163.1</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>24172.2</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>1144</v>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24172 | CE@24150 | NORMAL ATR=28 | risk=₹2340 (3.6%)</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W17" s="2" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="X17" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>13:57:45</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>14:13:24</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>24150</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>16282</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>24174.7</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>-2405</v>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24175 | CE@24150 | NORMAL ATR=28 | risk=₹2346 (3.5%)</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="X18" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2110,6 +2110,96 @@
         <v>0</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>10:46:46</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>10:50:10</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>23900</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>13741</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>-0.478</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>23899</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>-12</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>-3120</v>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>retest | SMA-2 Flow-3 | Nifty@23899 | PE@23900 | NORMAL ATR=27 | risk=₹3107 (4.9%)</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X19" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2200,6 +2200,1176 @@
         <v>1</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>11:44:41</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>11:54:27</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>23950</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>3721</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>23932</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>-682</v>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>retest | SMA-2 Flow-1 | Nifty@23932 | PE@23950 | NORMAL+REPEAT1 ATR=27 | risk=₹666 (1.1%)</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X20" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>11:55:04</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>11:58:10</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>4865</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>-0.634</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>23941.8</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>BREAKEVEN</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23942 | PE@24000 ITM24000 | NORMAL+REPEAT2 ATR=27 | risk=₹549 (0.9%)</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W21" s="4" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X21" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>11:58:43</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>12:01:07</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>4784</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>-0.649</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>23943.3</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23943 | PE@24000 ITM24000 | NORMAL+REPEAT3 ATR=27 | risk=₹429 (0.7%)</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X22" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>12:01:23</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>12:02:18</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>4953</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>-0.672</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>23938.9</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23939 | PE@24000 ITM24000 | NORMAL+REPEAT4 ATR=27 | risk=₹312 (0.5%)</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X23" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>12:02:27</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>12:03:24</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>23950</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>3296</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>-0.494</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>23933.5</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>-332</v>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23933 | PE@23950 | NORMAL+REPEAT5 ATR=27 | risk=₹312 (0.5%)</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X24" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>12:03:37</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>12:04:48</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>5265</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>-0.668</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>23937.5</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>BREAKEVEN</t>
+        </is>
+      </c>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23937 | PE@24000 ITM24000 | NORMAL+REPEAT6 ATR=27 | risk=₹312 (0.6%)</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U25" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X25" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>12:04:51</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>12:05:10</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>5288</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>-0.672</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>23935.7</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23936 | PE@24000 ITM24000 | NORMAL+REPEAT7 ATR=27 | risk=₹315 (0.6%)</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X26" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>12:05:13</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>12:06:05</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>23950</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>3263</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>-0.532</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>23934.8</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23935 | PE@23950 | NORMAL+REPEAT8 ATR=27 | risk=₹312 (0.6%)</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W27" s="2" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X27" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>12:06:18</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>12:06:48</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>23950</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>3536</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>-0.5570000000000001</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>23930.2</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>-338</v>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23930 | PE@23950 | NORMAL+REPEAT9 ATR=27 | risk=₹312 (0.6%)</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X28" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>12:07:01</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>12:09:07</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>23950</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>3282</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>-0.531</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>23931.6</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>-39</v>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23932 | PE@23950 | NORMAL+REPEAT10 ATR=27 | risk=₹312 (0.6%)</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X29" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>12:09:09</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>12:12:25</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>23950</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>3270</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>-0.554</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>23931.5</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>-32</v>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23931 | PE@23950 | NORMAL+REPEAT11 ATR=27 | risk=₹312 (0.6%)</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X30" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>12:12:32</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>12:12:45</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>5356</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>-0.709</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>23929</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23929 | PE@24000 ITM24000 | NORMAL+REPEAT12 ATR=27 | risk=₹312 (0.6%)</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X31" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>12:12:53</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>12:14:44</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>23950</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>3292</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>-0.539</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>23927.9</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23928 | PE@23950 | NORMAL+REPEAT13 ATR=27 | risk=₹309 (0.6%)</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X32" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X32"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3370,6 +3370,96 @@
         <v>1</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>12:52:19</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>12:54:04</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>4904</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>-0.664</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>23935.4</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>-793</v>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23935 | PE@24000 ITM24000 | NORMAL ATR=27 | risk=₹777 (1.2%)</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X33" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3460,6 +3460,366 @@
         <v>1</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>13:17:58</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>13:22:36</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>23950</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>2360</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>-0.501</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>23944.8</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>884</v>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>retest | SMA-1 Flow-3 | Nifty@23945 | PE@23950[EXPIRY ATM] | NORMAL+EXPIRY+REPEAT1 ATR=27 | risk=₹4719 (7.5%)</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>partial_target_partial</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X34" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>13:17:58</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>13:23:27</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>23950</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>2360</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>-0.501</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>23944.8</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>1086</v>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>retest | SMA-1 Flow-3 | Nifty@23945 | PE@23950[EXPIRY ATM] | NORMAL+EXPIRY+REPEAT1 ATR=27 | risk=₹4719 (7.5%)</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X35" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>13:41:36</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>23950</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>4810</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>-0.526</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>23938</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>-702</v>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23938 | PE@23950[EXPIRY ATM] | NORMAL+EXPIRY+REPEAT3 ATR=27 | risk=₹4810 (7.4%)</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X36" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>14:20:04</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>14:20:27</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>23900</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>4940</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>-0.575</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>23879.1</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@23879 | PE@23900[EXPIRY ATM] | NORMAL+EXPIRY+REPEAT4 ATR=27 | risk=₹4940 (7.7%)</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X37" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X37"/>
+  <dimension ref="A1:X42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3820,6 +3820,456 @@
         <v>1</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>12:11:35</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>13:02:41</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>24050</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>10494</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>143.4</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>197.4</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>24033.5</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>-1202</v>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24034 | CE@24050 | NORMAL ATR=33 | risk=₹1173 (1.8%)</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="X38" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>13:05:20</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>13:23:25</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>11125</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>201.8</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>24016.4</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>BREAKEVEN</t>
+        </is>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24016 | CE@24000 | NORMAL+REPEAT1 ATR=33 | risk=₹998 (1.6%)</t>
+        </is>
+      </c>
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="W39" s="4" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="X39" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>13:23:27</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>13:39:39</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>172.4</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>11209</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>159.8</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>197.6</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>24019.2</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>780</v>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24019 | CE@24000 | NORMAL+REPEAT2 ATR=33 | risk=₹822 (1.3%)</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W40" s="2" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="X40" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>13:41:03</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>14:00:11</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>24050</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>10140</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>24034.3</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>-663</v>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24034 | CE@24050 | NORMAL+REPEAT3 ATR=33 | risk=₹644 (1.0%)</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="X41" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>14:00:12</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>14:05:49</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>11216</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>24017.4</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24017 | CE@24000 | NORMAL+REPEAT4 ATR=33 | risk=₹465 (0.7%)</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="X42" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4270,6 +4270,366 @@
         <v>0</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>09:30:01</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>09:46:34</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>24100</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>167.4</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>9734</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>24109.2</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>1144</v>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+1 | Nifty@24109 | CE@24100 | NORMAL ATR=33 | risk=₹1167 (1.8%)</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="X43" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>09:51:35</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>10:03:06</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>24150</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>134.3</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>8730</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>24145.8</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>-1008</v>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>orb | SMA+2 Flow+1 | Nifty@24146 | CE@24150 | NORMAL+REPEAT1 ATR=33 | risk=₹994 (1.7%)</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="X44" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>10:36:05</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>10:46:26</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>24100</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>130.2</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>8460</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>149.1</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>24102.1</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>-39</v>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+1 | Nifty@24102 | CE@24100 | CONSOLIDATING+REPEAT2 ATR=19 | risk=₹816 (1.3%)</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X45" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>11:01:30</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>11:11:21</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>24100</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>8570</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>146.8</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>24111.6</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>-644</v>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+1 | Nifty@24112 | CE@24100 | CONSOLIDATING+REPEAT3 ATR=19 | risk=₹647 (1.0%)</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X46" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X46"/>
+  <dimension ref="A1:X51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4630,6 +4630,456 @@
         <v>0</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>10:16:36</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>10:39:37</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>24300</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>128.4</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>7917</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>24324</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>pdh_break | SMA+2 Flow+3 | Nifty@24324 | CE@24300 | CONSOLIDATING ATR=19 | risk=₹1170 (1.9%)</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W47" s="2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X47" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>10:44:45</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>10:56:05</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>24350</v>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>6428</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>24339.5</v>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>BREAKEVEN</t>
+        </is>
+      </c>
+      <c r="R48" s="4" t="inlineStr">
+        <is>
+          <t>pdh_break | SMA+2 Flow+3 | Nifty@24339 | CE@24350 | CONSOLIDATING+REPEAT1 ATR=19 | risk=₹663 (1.0%)</t>
+        </is>
+      </c>
+      <c r="S48" s="4" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T48" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="W48" s="4" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X48" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>11:59:15</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>12:21:14</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>24350</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>6747</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>24354.8</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>retest | SMA+2 Flow+3 | Nifty@24355 | CE@24350 | CONSOLIDATING+REPEAT2 ATR=12 | risk=₹819 (1.3%)</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W49" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="X49" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>12:50:19</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>13:01:56</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>24350</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>6656</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>24359.9</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>-696</v>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>retest | SMA+2 Flow+3 | Nifty@24360 | CE@24350 | CONSOLIDATING+REPEAT3 ATR=13 | risk=₹644 (1.0%)</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T50" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V50" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W50" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="X50" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>13:32:44</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>13:37:58</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>24300</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>6035</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>-0.474</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>24300</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>526</v>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@24300 | PE@24300 | CONSOLIDATING ATR=14 | risk=₹783 (1.2%)</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W51" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="X51" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5080,6 +5080,366 @@
         <v>0</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>10:26:51</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>10:51:51</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>24400</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>4690</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>24400.4</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24400 | CE@24400 | NORMAL ATR=22 | risk=₹777 (1.2%)</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>stale_exit_25min</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W52" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X52" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>10:56:53</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>11:08:13</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>24400</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>4778</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>24412.2</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>-13</v>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24412 | CE@24400 | CONSOLIDATING+REPEAT1 ATR=17 | risk=₹663 (1.1%)</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T53" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W53" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="X53" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>11:23:15</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>11:48:15</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>24400</v>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>4807</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>24416</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24416 | CE@24400 | CONSOLIDATING+REPEAT2 ATR=16 | risk=₹549 (0.9%)</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr">
+        <is>
+          <t>stale_exit_25min</t>
+        </is>
+      </c>
+      <c r="T54" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X54" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>12:48:22</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>13:13:22</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>24450</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>3780</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>24436.7</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24437 | CE@24450 | CONSOLIDATING+REPEAT3 ATR=11 | risk=₹432 (0.7%)</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>stale_exit_25min</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W55" s="2" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="X55" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X55"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5440,6 +5440,366 @@
         <v>0</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>10:00:02</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>10:05:42</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>24400</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>5333</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>24474</v>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>-84</v>
+      </c>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24474 | CE@24400 ITM24400 | NORMAL ATR=34 | risk=₹783 (1.2%)</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T56" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V56" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W56" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X56" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>10:32:49</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>10:44:51</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>24450</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>3448</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>24484.8</v>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="P57" s="3" t="n">
+        <v>-682</v>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>retest | SMA+2 Flow+3 | Nifty@24485 | CE@24450 ITM24450 | NORMAL+REPEAT1 ATR=21 | risk=₹666 (1.1%)</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T57" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="X57" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>11:44:52</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>11:47:00</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>24450</v>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>4326</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>24509.3</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>BREAKEVEN</t>
+        </is>
+      </c>
+      <c r="R58" s="4" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24509 | CE@24450 ITM24450 | CONSOLIDATING+REPEAT2 ATR=16 | risk=₹549 (0.9%)</t>
+        </is>
+      </c>
+      <c r="S58" s="4" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T58" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="W58" s="4" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X58" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>12:10:00</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>12:12:18</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>24450</v>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>4680</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>24520.2</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>-442</v>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24520 | CE@24450 ITM24450 | CONSOLIDATING+REPEAT3 ATR=13 | risk=₹429 (0.7%)</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T59" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="X59" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5800,6 +5800,276 @@
         <v>1</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>10:12:49</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>10:28:58</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>154.2</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>153.7</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>10020</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>136.2</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>190.2</v>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>-0.482</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>24245.3</v>
+      </c>
+      <c r="O60" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P60" s="3" t="n">
+        <v>-32</v>
+      </c>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>retest | SMA-2 Flow-1 | Nifty@24245 | PE@24250 | NORMAL ATR=30 | risk=₹1167 (1.9%)</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T60" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U60" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V60" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W60" s="3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="X60" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>12:10:20</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>12:18:23</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>137.2</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>8921</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>160.2</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>-0.458</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>24224.8</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>-13</v>
+      </c>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@24225 | PE@24200 | CONSOLIDATING+REPEAT1 ATR=16 | risk=₹991 (1.6%)</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T61" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W61" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X61" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>13:21:10</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>13:39:29</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>8658</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>152.1</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>-0.462</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>24218.4</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>retest | SMA-1 Flow-3 | Nifty@24218 | PE@24200 | CONSOLIDATING+REPEAT2 ATR=17 | risk=₹819 (1.3%)</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T62" s="3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U62" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V62" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W62" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X62" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6070,6 +6070,186 @@
         <v>0</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>13:25:54</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>13:30:40</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>24050</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>9425</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>-0.506</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>24031.3</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>-663</v>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>retest | SMA-2 Flow-3 | Nifty@24031 | PE@24050 | CONSOLIDATING ATR=19 | risk=₹1170 (1.9%)</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr">
+        <is>
+          <t>mae_exit_10min</t>
+        </is>
+      </c>
+      <c r="T63" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U63" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V63" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W63" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X63" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>14:11:26</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>14:15:06</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>24050</v>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>131.7</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>9246</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>165.2</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>-0.505</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>24040.8</v>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>-682</v>
+      </c>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>retest | SMA+0 Flow-3 | Nifty@24041 | PE@24050 | CONSOLIDATING+REPEAT1 ATR=19 | risk=₹991 (1.6%)</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr">
+        <is>
+          <t>mae_exit_10min</t>
+        </is>
+      </c>
+      <c r="T64" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W64" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X64" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6250,6 +6250,96 @@
         <v>0</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>10:37:23</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>10:41:50</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>7312</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>24202.3</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>orb | SMA+2 Flow+1 | Nifty@24202 | CE@24200 | CONSOLIDATING ATR=16 | risk=₹1170 (1.9%)</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X65" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6340,6 +6340,96 @@
         <v>0</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>09:30:57</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>09:36:49</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>24050</v>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>7267</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>24028</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>-650</v>
+      </c>
+      <c r="Q66" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@24028 | PE@24050 | NORMAL ATR=32 | risk=₹1170 (1.9%)</t>
+        </is>
+      </c>
+      <c r="S66" s="3" t="inlineStr">
+        <is>
+          <t>mae_exit_10min</t>
+        </is>
+      </c>
+      <c r="T66" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W66" s="3" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="X66" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X66"/>
+  <dimension ref="A1:X67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6430,6 +6430,96 @@
         <v>0</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>12:46:55</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>12:51:39</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>5993</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>24213.2</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24213 | CE@24200 | CONSOLIDATING ATR=20 | risk=₹780 (1.3%)</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W67" s="2" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="X67" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X11"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1497,6 +1497,726 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>09:30:30</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>09:55:30</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>10491</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>143.4</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>197.4</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>24205.2</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>-318</v>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24205 | CE@24200 | NORMAL ATR=29 | risk=₹1170 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>stale_exit_25min</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="X12" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>09:30:30</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>09:55:30</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>10491</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>143.4</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>197.4</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>24205.2</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>-318</v>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA+2 Flow+3 | Nifty@24205 | CE@24200 | NORMAL ATR=29 | risk=₹1170 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>stale_exit_25min</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="X13" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>12:54:26</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12:54:52</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>24150</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>10952</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>-0.516</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>24131.3</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>momentum | SMA-2 Flow-3 | Nifty@24131 | PE@24150 | CONSOLIDATING ATR=16 | risk=₹1170 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X14" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>12:54:26</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>12:54:52</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>24150</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>10952</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>-0.516</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>24131.3</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>momentum | SMA-2 Flow-3 | Nifty@24131 | PE@24150 | CONSOLIDATING ATR=16 | risk=₹1170 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W15" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X15" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>12:59:53</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>13:00:07</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>24050</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>11879</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>167.4</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>205.8</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>-0.503</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>24051.7</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>orb | SMA-2 Flow-3 | Nifty@24052 | PE@24050 | CONSOLIDATING+REPEAT1 ATR=16 | risk=₹998 (2.0%)</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="X16" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>12:59:53</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>13:00:07</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>24050</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>11879</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>167.4</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>205.8</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>-0.503</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>24051.7</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>orb | SMA-2 Flow-3 | Nifty@24052 | PE@24050 | CONSOLIDATING+REPEAT1 ATR=16 | risk=₹998 (2.0%)</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W17" s="2" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="X17" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>13:15:09</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>13:15:54</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>24050</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>168.2</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>11622</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>-0.501</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>24049.8</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>-689</v>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@24050 | PE@24050 | NORMAL+REPEAT2 ATR=27 | risk=₹819 (1.7%)</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>mae_exit_10min</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="X18" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>13:15:09</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>13:15:54</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>24050</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>168.2</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>11622</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>-0.501</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>24049.8</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>-689</v>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@24050 | PE@24050 | NORMAL+REPEAT2 ATR=27 | risk=₹819 (1.7%)</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>mae_exit_10min</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="X19" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2217,6 +2217,186 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>13:31:29</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>13:34:52</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>24050</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>166.8</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>10605</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>-0.482</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>24070.9</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@24071 | PE@24050 | NORMAL+REPEAT3 ATR=29 | risk=₹647 (1.3%)</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W20" s="2" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="X20" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>13:31:29</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>13:34:52</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>24050</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>166.8</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>10605</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>-0.482</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>24070.9</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>sustained | SMA-2 Flow-3 | Nifty@24071 | PE@24050 | NORMAL+REPEAT3 ATR=29 | risk=₹647 (1.3%)</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W21" s="2" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="X21" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2397,6 +2397,186 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>13:30:13</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>13:32:35</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>24100</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>139.6</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>9074</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>166.6</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>-0.485</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>24091.5</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>range_break | SMA-2 Flow-3 | Nifty@24092 | PE@24100 | CONSOLIDATING ATR=13 | risk=₹1170 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="X22" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>13:30:13</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>13:32:35</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>24100</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>139.6</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>9074</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>166.6</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>-0.485</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>24091.5</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>range_break | SMA-2 Flow-3 | Nifty@24092 | PE@24100 | CONSOLIDATING ATR=13 | risk=₹1170 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="X23" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2577,6 +2577,366 @@
         <v>0</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>09:25:41</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>09:44:23</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>7868</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>157.1</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>24202</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>pdh_break | SMA+2 Flow+3 | Nifty@24202 | CE@24200 | NORMAL ATR=26 | risk=₹1173 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W24" s="2" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="X24" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>09:25:41</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>09:44:23</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>7868</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>157.1</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>24202</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>pdh_break | SMA+2 Flow+3 | Nifty@24202 | CE@24200 | NORMAL ATR=26 | risk=₹1173 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W25" s="2" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="X25" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>09:50:40</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>09:56:20</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>7238</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>141.9</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>24242.8</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>-650</v>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>orb | SMA+2 Flow+3 | Nifty@24243 | CE@24250 | NORMAL+REPEAT1 ATR=29 | risk=₹998 (2.0%)</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>mae_exit_10min</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="X26" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>09:50:40</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>09:56:20</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>7238</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>141.9</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>24242.8</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>-650</v>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>orb | SMA+2 Flow+3 | Nifty@24243 | CE@24250 | NORMAL+REPEAT1 ATR=29 | risk=₹998 (2.0%)</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>mae_exit_10min</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="X27" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:X47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2937,6 +2937,1806 @@
         <v>0</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>09:32:48</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>09:40:59</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>7560</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>152.3</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>-0.539</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>24175.5</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA-2 Flow-3 | Nifty@24176 | PE@24200 | NORMAL ATR=30 | risk=₹1170 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W28" s="2" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X28" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>09:32:48</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>09:40:59</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>7560</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>152.3</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>-0.539</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>24175.5</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA-2 Flow-3 | Nifty@24176 | PE@24200 | NORMAL ATR=30 | risk=₹1170 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W29" s="2" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="X29" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>10:40:01</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>7358</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>143.8</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>24225.6</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>-26</v>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA-1 Flow-1 | Nifty@24226 | PE@24250 | NORMAL+REPEAT1 ATR=22 | risk=₹994 (2.1%)</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t>signal_flip</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X30" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>10:40:01</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>7358</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>143.8</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>24225.6</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>-26</v>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA-1 Flow-1 | Nifty@24226 | PE@24250 | NORMAL+REPEAT1 ATR=22 | risk=₹994 (2.1%)</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>signal_flip</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X31" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>10:50:15</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>10:51:27</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>5759</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>24224.9</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA+0 Flow+3 | Nifty@24225 | CE@24200 | CONSOLIDATING ATR=19 | risk=₹780 (1.6%)</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>direction_change</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X32" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>10:50:15</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>10:51:27</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>5759</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>24224.9</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA+0 Flow+3 | Nifty@24225 | CE@24200 | CONSOLIDATING ATR=19 | risk=₹780 (1.6%)</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>direction_change</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X33" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>11:29:32</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>11:35:56</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>6052</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>24206.4</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA-2 Flow-1 | Nifty@24206 | PE@24200 | CONSOLIDATING ATR=17 | risk=₹780 (1.6%)</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X34" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>11:29:32</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>11:35:56</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>6052</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>24206.4</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA-2 Flow-1 | Nifty@24206 | PE@24200 | CONSOLIDATING ATR=17 | risk=₹780 (1.6%)</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X35" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>11:55:00</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>11:59:15</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>7014</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>-0.539</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>24179.8</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>-670</v>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-2 Flow-1 | Nifty@24180 | PE@24200 | CONSOLIDATING+REPEAT1 ATR=16 | risk=₹994 (2.1%)</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t>mae_exit_10min</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X36" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>11:55:00</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>11:59:15</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>7014</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>-0.539</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>24179.8</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>-670</v>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-2 Flow-1 | Nifty@24180 | PE@24200 | CONSOLIDATING+REPEAT1 ATR=16 | risk=₹994 (2.1%)</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t>mae_exit_10min</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X37" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>12:45:03</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>12:47:59</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>24150</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>5480</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>-0.484</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>24157.5</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>910</v>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>TARGET_HIT</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-2 Flow-1 | Nifty@24158 | PE@24150 | CONSOLIDATING+REPEAT2 ATR=15 | risk=₹546 (1.1%)</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>target_volatile</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W38" s="2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="X38" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>12:45:03</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>12:47:59</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>24150</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>5480</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>-0.484</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>24157.5</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>910</v>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>TARGET_HIT</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-2 Flow-1 | Nifty@24158 | PE@24150 | CONSOLIDATING+REPEAT2 ATR=15 | risk=₹546 (1.1%)</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>target_volatile</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W39" s="2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="X39" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>13:15:01</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>13:15:19</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>4440</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>24225.1</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA+2 Flow+1 | Nifty@24225 | CE@24250 | CONSOLIDATING ATR=18 | risk=₹780 (1.6%)</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="X40" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>13:15:01</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>13:15:19</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>4440</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>24225.1</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA+2 Flow+1 | Nifty@24225 | CE@24250 | CONSOLIDATING ATR=18 | risk=₹780 (1.6%)</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="X41" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>13:30:20</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>13:41:41</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>5210</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>24245</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>-696</v>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA+2 Flow+1 | Nifty@24245 | CE@24250 | NORMAL+REPEAT1 ATR=20 | risk=₹660 (1.4%)</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="X42" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>13:30:20</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>13:41:41</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>5210</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>24245</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>-696</v>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA+2 Flow+1 | Nifty@24245 | CE@24250 | NORMAL+REPEAT1 ATR=20 | risk=₹660 (1.4%)</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="X43" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>14:00:02</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>14:05:15</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>5444</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>24253.8</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA+2 Flow+1 | Nifty@24254 | CE@24250 | NORMAL+REPEAT2 ATR=21 | risk=₹549 (1.1%)</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X44" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>14:00:02</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>14:05:15</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>5444</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>24253.8</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA+2 Flow+1 | Nifty@24254 | CE@24250 | NORMAL+REPEAT2 ATR=21 | risk=₹549 (1.1%)</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X45" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>15:10:44</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>15:16:45</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>4660</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>24238.2</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>-13</v>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA+1 Flow+2 | Nifty@24238 | CE@24250 | CONSOLIDATING+REPEAT3 ATR=14 | risk=₹429 (0.9%)</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X46" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>15:10:44</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>15:16:45</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>4660</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>24238.2</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>-13</v>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA+1 Flow+2 | Nifty@24238 | CE@24250 | CONSOLIDATING+REPEAT3 ATR=14 | risk=₹429 (0.9%)</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W47" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X47" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X47"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4737,6 +4737,1446 @@
         <v>0</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>09:50:11</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>09:50:40</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>3682</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>-0.594</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>24225</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-1 Flow-1 | Nifty@24225 | PE@24250 | NORMAL ATR=21 | risk=₹783 (1.6%)</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>signal_flip</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W48" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X48" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>09:50:11</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>09:50:40</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>3682</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>-0.594</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>24225</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-1 Flow-1 | Nifty@24225 | PE@24250 | NORMAL ATR=21 | risk=₹783 (1.6%)</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>signal_flip</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W49" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X49" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>10:15:01</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>10:16:05</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>4270</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>-0.629</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>24212.5</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>-32</v>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-2 Flow-1 | Nifty@24212 | PE@24250 ITM24250 | NORMAL+REPEAT1 ATR=22 | risk=₹663 (1.4%)</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T50" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U50" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V50" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W50" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X50" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>10:15:01</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>10:16:05</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>4270</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>-0.629</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>24212.5</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>-32</v>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-2 Flow-1 | Nifty@24212 | PE@24250 ITM24250 | NORMAL+REPEAT1 ATR=22 | risk=₹663 (1.4%)</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T51" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W51" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X51" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>10:28:27</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>5138</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>-0.701</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>24193.4</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="P52" s="3" t="n">
+        <v>-13</v>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA-2 Flow-1 | Nifty@24193 | PE@24250 ITM24250 | NORMAL+REPEAT2 ATR=22 | risk=₹549 (1.1%)</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T52" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U52" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V52" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W52" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X52" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>10:28:27</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>24250</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>5138</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>-0.701</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>24193.4</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>-13</v>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA-2 Flow-1 | Nifty@24193 | PE@24250 ITM24250 | NORMAL+REPEAT2 ATR=22 | risk=₹549 (1.1%)</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T53" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U53" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V53" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W53" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X53" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>3315</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>-0.542</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>24188.4</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>644</v>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>TARGET_HIT</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>lux_retest | SMA-2 Flow-1 | Nifty@24188 | PE@24200 | CONSOLIDATING+REPEAT3 ATR=19 | risk=₹429 (0.9%)</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>target_volatile</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W54" s="2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X54" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>10:38:57</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>3315</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>-0.542</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>24188.4</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>644</v>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>TARGET_HIT</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>lux_retest | SMA-2 Flow-1 | Nifty@24188 | PE@24200 | CONSOLIDATING+REPEAT3 ATR=19 | risk=₹429 (0.9%)</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>target_volatile</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W55" s="2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X55" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>11:46:03</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>11:46:48</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>3848</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>-0.663</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>24159</v>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>-318</v>
+      </c>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-2 Flow-1 | Nifty@24159 | PE@24200 ITM24200 | CONSOLIDATING+REPEAT4 ATR=16 | risk=₹312 (0.6%)</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T56" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U56" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V56" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W56" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X56" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>11:46:03</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>11:46:48</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>3848</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>-0.663</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>24159</v>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="P57" s="3" t="n">
+        <v>-318</v>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>SL_HIT</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-2 Flow-1 | Nifty@24159 | PE@24200 ITM24200 | CONSOLIDATING+REPEAT4 ATR=16 | risk=₹312 (0.6%)</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T57" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U57" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V57" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W57" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X57" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>14:17:16</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>14:17:47</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>24150</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>-0.411</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>24160</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>358</v>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>lux_retest | SMA-2 Flow-1 | Nifty@24160 | PE@24150[EXPIRY ATM] | CONSOLIDATING+EXPIRY+REPEAT5 ATR=13 | risk=₹4615 (9.6%)</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U58" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W58" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="X58" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>14:17:16</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>14:17:47</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>24150</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>-0.411</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>24160</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>358</v>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>lux_retest | SMA-2 Flow-1 | Nifty@24160 | PE@24150[EXPIRY ATM] | CONSOLIDATING+EXPIRY+REPEAT5 ATR=13 | risk=₹4615 (9.6%)</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U59" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W59" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="X59" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>09:20:02</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>10:05:50</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>24100</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>171.4</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>199.6</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>11141</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>153.4</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>243.8</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>-0.514</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>24095.8</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>1833</v>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-2 Flow-1 | Nifty@24096 | PE@24100 | NORMAL ATR=22 | risk=₹1170 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W60" s="2" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X60" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>09:20:02</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>10:05:50</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>24100</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>171.4</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>199.6</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>11141</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>153.4</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>243.8</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>-0.514</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>24095.8</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>1833</v>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-2 Flow-1 | Nifty@24096 | PE@24100 | NORMAL ATR=22 | risk=₹1170 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U61" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W61" s="2" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X61" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>10:20:52</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>10:28:28</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>151.8</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>166.6</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>9867</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>-0.488</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>24019.3</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>962</v>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-2 Flow-1 | Nifty@24019 | PE@24000 | NORMAL+REPEAT1 ATR=29 | risk=₹994 (2.0%)</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U62" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W62" s="2" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="X62" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>10:20:52</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>10:28:28</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>151.8</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>166.6</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>9867</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>-0.488</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>24019.3</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>962</v>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>lux_break | SMA-2 Flow-1 | Nifty@24019 | PE@24000 | NORMAL+REPEAT1 ATR=29 | risk=₹994 (2.0%)</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U63" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W63" s="2" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="X63" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trades.xlsx
+++ b/logs/trades.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X69"/>
+  <dimension ref="A1:X75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6717,6 +6717,546 @@
         <v>0</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>09:48:51</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>09:53:04</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>23650</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>7852</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>174.8</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>-0.462</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>23647.8</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>orb | SMA-2 Flow-1 | Nifty@23648 | PE@23650 | TRENDING ATR=41 | risk=₹1170 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U70" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V70" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W70" s="2" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="X70" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>09:48:51</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>09:53:04</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>23650</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>7852</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>174.8</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>-0.462</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>23647.8</v>
+      </c>
+      <c r="O71" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>orb | SMA-2 Flow-1 | Nifty@23648 | PE@23650 | TRENDING ATR=41 | risk=₹1170 (2.4%)</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U71" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V71" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W71" s="2" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="X71" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>10:55:11</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>11:02:49</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>23650</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>8021</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>146.4</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>-0.465</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>23634.5</v>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA-2 Flow-1 | Nifty@23635 | PE@23650 | CONSOLIDATING+REPEAT1 ATR=19 | risk=₹994 (2.0%)</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U72" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W72" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="X72" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>10:55:11</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>11:02:49</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>23650</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>8021</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>146.4</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>-0.465</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>23634.5</v>
+      </c>
+      <c r="O73" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>lux_bounce | SMA-2 Flow-1 | Nifty@23635 | PE@23650 | CONSOLIDATING+REPEAT1 ATR=19 | risk=₹994 (2.0%)</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>trail_sl</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U73" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V73" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W73" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="X73" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>14:05:01</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>14:10:11</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>23800</v>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>9233</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>178.1</v>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>23816.8</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>-696</v>
+      </c>
+      <c r="Q74" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R74" s="3" t="inlineStr">
+        <is>
+          <t>lux_break | SMA+2 Flow+1 | Nifty@23817 | CE@23800 | NORMAL ATR=21 | risk=₹1167 (2.3%)</t>
+        </is>
+      </c>
+      <c r="S74" s="3" t="inlineStr">
+        <is>
+          <t>mae_exit_10min</t>
+        </is>
+      </c>
+      <c r="T74" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W74" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="X74" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>14:05:01</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>14:10:11</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>23800</v>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>9233</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>178.1</v>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>23816.8</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>-696</v>
+      </c>
+      <c r="Q75" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>lux_break | SMA+2 Flow+1 | Nifty@23817 | CE@23800 | NORMAL ATR=21 | risk=₹1167 (2.3%)</t>
+        </is>
+      </c>
+      <c r="S75" s="3" t="inlineStr">
+        <is>
+          <t>mae_exit_10min</t>
+        </is>
+      </c>
+      <c r="T75" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W75" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="X75" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
